--- a/manuscript_outputs/v1_0_20260501/M038_v2_DATA_AND_SOURCES.xlsx
+++ b/manuscript_outputs/v1_0_20260501/M038_v2_DATA_AND_SOURCES.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +82,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -149,6 +160,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -988,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1747,6 +1773,135 @@
         <v>8</v>
       </c>
     </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_split</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>05_Table4_Complications (hypopara split)</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>WITH base AS (
+  SELECT research_id, (composite is_massive expression) AS is_massive
+  FROM manuscript_workspace.cohort_m038_massive_goiter_v1
+)
+SELECT is_massive,
+  COUNT(*) FILTER (WHERE cpm.comp_hypoparathyroidism_confirmed AND cpm.comp_hypoparathyroidism_transient) AS hpt_transient,
+  COUNT(*) FILTER (WHERE cpm.comp_hypoparathyroidism_confirmed AND cpm.comp_hypoparathyroidism_permanent) AS hpt_permanent,
+  COUNT(*) FILTER (WHERE cpm.comp_hypoparathyroidism_confirmed AND NOT cpm.comp_hypoparathyroidism_transient AND NOT cpm.comp_hypoparathyroidism_permanent) AS hpt_unclassified
+FROM base b JOIN main.canonical_patient_master cpm USING (research_id)
+GROUP BY is_massive;</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>main.canonical_patient_master + cohort_m038_massive_goiter_v1</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Q05b_hca_preop</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>05_Table4_Complications (hypocalcemia preop)</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>(see Q05b_hpt_split JOIN; FILTER WHERE cpm.comp_hypocalcemia_timing_window = 'pre_surgery')</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>main.canonical_patient_master + cohort_m038_massive_goiter_v1</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Q05b_preop_gap</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>05_Table4_Complications (RLN/VC preop)</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Encoding gap — no preop column on canonical_patient_master for RLN injury or VC paralysis. Carry-forwards: CF-RLN-PREOP-FLAG, CF-VC-PARALYSIS-PREOP-FLAG.</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>main.canonical_patient_master</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_preexist</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>05_Table4_Complications (hypopara preexisting FYI)</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>(see Q05b_hpt_split JOIN; FILTER WHERE cpm.comp_hypoparathyroidism_preexisting)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>main.canonical_patient_master + cohort_m038_massive_goiter_v1</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5107,7 +5262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5545,7 +5700,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>(to be filled at commit time)</t>
+          <t>b232007 (initial); follow-up commit (this update) — see git log</t>
         </is>
       </c>
     </row>
@@ -5653,6 +5808,89 @@
       <c r="B52" s="6" t="inlineStr">
         <is>
           <t>PASS (100% massive; 99.98% non-massive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <f>== Standing rule applied 2026-05-01 (post-initial-audit) ===</f>
+        <v/>
+      </c>
+      <c r="B54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>memory/feedback_complications_transient_vs_permanent.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism layout</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Split: postop transient (&lt;6mo) + postop permanent (&gt;6mo). M038: 83+4=87 / 197+12=209.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Hypocalcemia layout</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Postop confirmed + 'present preop' row (timing_window='pre_surgery'). M038 preop: 7 / 46.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RLN injury layout</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Postop confirmed only; preop flag awaiting CF-RLN-PREOP-FLAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>VC paralysis layout</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Postop confirmed only; preop flag awaiting CF-VC-PARALYSIS-PREOP-FLAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Cohort-wide hypopara partition validation</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>296 confirmed → 280 transient (94.6%) + 16 permanent (5.4%); zero unclassified.</t>
         </is>
       </c>
     </row>
@@ -8134,22 +8372,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>§3.5 Table 4 — Strict-definition perioperative complications (post-mig_252 rollup). Strict definition: comp_*_confirmed = TRUE ⇔ underlying finding_status='present' AND evidence_strength IN ('definitive','probable'). Denominators: massive 2,501; non-massive 8,370.</t>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>§3.5 Table 4 — Strict-definition perioperative complications (post-mig_252 rollup), restructured per the standing rule (memory/feedback_complications_transient_vs_permanent.md). Hypoparathyroidism is split into transient (&lt;6mo) vs permanent (&gt;6mo). Hypocalcemia, RLN injury, VC paresis, and VC paralysis report postop confirmed plus a 'present preop' flag row (encoding gaps noted). Strict postop definition: comp_*_confirmed = TRUE ⇔ underlying finding_status='present' AND evidence_strength IN ('definitive','probable'). Denominators: massive 2,501; non-massive 8,370.</t>
         </is>
       </c>
     </row>
@@ -8189,63 +8428,48 @@
           <t>Source query</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="16">
+        <f>== Postop confirmed (whole-arm denominator) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Any confirmed complication flag</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B5" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C5" s="8" t="n">
         <v>0.05277888844462215</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D5" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E5" s="8" t="n">
         <v>0.03201911589008363</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F5" s="12" t="n">
         <v>1.648355583139878</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed RLN injury</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0.005597760895641743</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0008363201911589009</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>6.693322670931627</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Q05_comps</t>
-        </is>
-      </c>
+      <c r="H5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Confirmed hematoma</t>
         </is>
@@ -8265,14 +8489,15 @@
       <c r="F6" s="12" t="n">
         <v>1.710515793682527</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
+      <c r="H6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Confirmed seroma</t>
         </is>
@@ -8292,14 +8517,15 @@
       <c r="F7" s="12" t="n">
         <v>1.487405037984806</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
+      <c r="H7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Confirmed chyle leak</t>
         </is>
@@ -8319,16 +8545,17 @@
       <c r="F8" s="12" t="n">
         <v>6.693322670931628</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
+      <c r="H8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed VC paresis</t>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed VC paresis (postop)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -8343,17 +8570,22 @@
       <c r="E9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Standing rule: preop flag not encoded; CF-VC-PARALYSIS-PREOP-FLAG</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed VC paralysis</t>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed VC paralysis (postop)</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -8371,68 +8603,83 @@
       <c r="F10" s="12" t="n">
         <v>15.89664134346262</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Standing rule: preop flag not encoded; CF-VC-PARALYSIS-PREOP-FLAG</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed hypocalcemia</t>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed RLN injury (postop)</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>0.005597760895641743</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.0008363201911589009</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>6.693322670931627</v>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Q05_comps</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Standing rule: preop flag not encoded; CF-RLN-PREOP-FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed hypocalcemia (postop)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C12" s="8" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E12" s="8" t="n">
         <v>0.0009557945041816009</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.4183326669332267</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed hypoparathyroidism</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0.03478608556577369</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>209</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.02497013142174433</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1.393107828638879</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Q05_comps</t>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Excludes preop cases (see preop row below)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>All-cause in-record mortality</t>
         </is>
@@ -8452,22 +8699,290 @@
       <c r="F13" s="12" t="n">
         <v>1.484609163853255</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Q05_comps</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Footer: Strict-definition rollup applied via mig_252 (commit 32beb7b). Pre-mig_252 rollups counted negation evidence (finding_status='absent') as confirmation; corrected expression requires finding_status='present' AND evidence_strength IN ('definitive','probable'). Cohort-wide impact: any_confirmed_complication_flag count 2,490 → 400 (validated 2026-05-01).</t>
+      <c r="H13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16">
+        <f>== Hypoparathyroidism — transient/permanent split (standing rule) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism — postop transient (&lt;6mo)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0.03318672530987605</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>197</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.02353643966547192</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1.410014674333312</v>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_split</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>comp_hypoparathyroidism_confirmed AND comp_hypoparathyroidism_transient</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism — postop permanent (&gt;6mo)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0.001599360255897641</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.001433691756272401</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1.115553778488604</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_split</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>comp_hypoparathyroidism_confirmed AND comp_hypoparathyroidism_permanent</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism — postop unclassified</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_split</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>Zero unclassified in M038; partition is clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism — postop ALL (sum check)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>0.03478608556577369</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>209</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.02497013142174433</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1.393107828638879</v>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Q05_comps</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>Sum check: 83+4=87 ✓; 197+12=209 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16">
+        <f>== Preop yes/no flag (standing rule) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Hypocalcemia — present preop</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0.002798880447820872</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.005495818399044205</v>
+      </c>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_hca_preop</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>comp_hypocalcemia_timing_window = 'pre_surgery'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>RLN injury — present preop</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_preop_gap</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>Not currently encoded — CF-RLN-PREOP-FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>VC paralysis — present preop</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_preop_gap</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Not currently encoded — CF-VC-PARALYSIS-PREOP-FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>VC paresis — present preop</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_preop_gap</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>Not currently encoded — same carry-forward as VC paralysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Hypoparathyroidism — preexisting (FYI)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.006797281087564974</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.005017921146953405</v>
+      </c>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Q05b_hpt_preexist</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>comp_hypoparathyroidism_preexisting; not used in trans/perm split (those count NEW postop cases only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Strict postop rollup applied via mig_252 (commit 32beb7b). Pre-mig_252 rollups counted negation evidence (finding_status='absent') as confirmation; corrected expression requires finding_status='present' AND evidence_strength IN ('definitive','probable'). Cohort-wide impact: any_confirmed_complication_flag count 2,490 → 400 (validated 2026-05-01). Hypoparathyroidism transient/permanent partition validated cohort-wide: 296 confirmed → 280 transient (94.6%) + 16 permanent (5.4%); zero unclassified. 14 confirmed cases have a permanence-classification limitation note ('followup_too_short_for_permanence_classification', 'reset_20260417:confirmed_duration_unknown', 'confirmed_hypopara_no_persistent_biochem_evidence_followup_gt_6mo'). 87% of confirmed cases have timing_window='unknown'; trans/perm assignment uses additional signals (treatment_req, biochem persistence, NSQIP recovered_flag) beyond pure timing. Standing rule reference: memory/feedback_complications_transient_vs_permanent.md.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:G15"/>
+  <mergeCells count="4">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A25:H25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
